--- a/uploads_templates/uploads_for_validation/7.plant_resource_requirements.xlsx
+++ b/uploads_templates/uploads_for_validation/7.plant_resource_requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Moove\RCCP\uploads_templates\uploads_for_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E827E3F-7E01-4E19-A3E8-F2FF38C6C696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57BCB71-86AC-4A53-8952-8F62CD99CBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-17580" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Manufacturing plant code (e.g. A1, A2). Must exist in the masterdata.</t>
   </si>
@@ -87,6 +87,18 @@
   </si>
   <si>
     <t>Plant 1</t>
+  </si>
+  <si>
+    <t>Plant 2</t>
+  </si>
+  <si>
+    <t>Plant 3</t>
+  </si>
+  <si>
+    <t>Plant 4</t>
+  </si>
+  <si>
+    <t>Plant 5</t>
   </si>
 </sst>
 </file>
@@ -503,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -561,6 +573,138 @@
         <v>8</v>
       </c>
       <c r="C5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3">
         <v>1</v>
       </c>
     </row>
